--- a/artfynd/A 41442-2023 artfynd.xlsx
+++ b/artfynd/A 41442-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41442-2023 artfynd.xlsx
+++ b/artfynd/A 41442-2023 artfynd.xlsx
@@ -1306,7 +1306,7 @@
         <v>118022032</v>
       </c>
       <c r="B7" t="n">
-        <v>103349</v>
+        <v>103351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 41442-2023 artfynd.xlsx
+++ b/artfynd/A 41442-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,253 +1301,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>118022032</v>
-      </c>
-      <c r="B7" t="n">
-        <v>103360</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>220164</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Solvända</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Helianthemum nummularium</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Spenörtsbeståndet, Århult V Oskarshamn, Sm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>578046</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6347708</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Oskarshamn</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Döderhult</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Leon Axelsson Widén</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Leon Axelsson Widén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>118223438</v>
-      </c>
-      <c r="B8" t="n">
-        <v>44525</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>102018</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Zygaena lonicerae</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Spenörtsbeståndet, Århult V Oskarshamn, Sm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>578046</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6347708</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Oskarshamn</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Döderhult</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-07-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Leon Axelsson Widén</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Leon Axelsson Widén</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41442-2023 artfynd.xlsx
+++ b/artfynd/A 41442-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66630228</v>
+        <v>110542084</v>
       </c>
       <c r="B2" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102021</v>
+        <v>102018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578045.6145036576</v>
+        <v>578046</v>
       </c>
       <c r="R2" t="n">
-        <v>6347707.986212344</v>
+        <v>6347708</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,22 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-09</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-09</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +777,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,22 +789,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Leon Axelsson Widén</t>
+          <t>Leon Axelsson Widén, Sture Ljungblom</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110288930</v>
+        <v>110542050</v>
       </c>
       <c r="B3" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,31 +807,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>102019</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578045.6145036576</v>
+        <v>578046</v>
       </c>
       <c r="R3" t="n">
-        <v>6347707.986212344</v>
+        <v>6347708</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,15 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110289041</v>
+        <v>66630228</v>
       </c>
       <c r="B4" t="n">
-        <v>41765</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,16 +928,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100768</v>
+        <v>102021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flenörtskapuschongfly</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cucullia scrophulariae</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,15 +947,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
@@ -978,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578045.6145036576</v>
+        <v>578046</v>
       </c>
       <c r="R4" t="n">
-        <v>6347707.986212344</v>
+        <v>6347708</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,22 +995,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2017-07-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2017-07-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1019,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1051,15 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110542050</v>
+        <v>110288930</v>
       </c>
       <c r="B5" t="n">
-        <v>44334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,36 +1048,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102019</v>
+        <v>220164</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578045.6145036576</v>
+        <v>578046</v>
       </c>
       <c r="R5" t="n">
-        <v>6347707.986212344</v>
+        <v>6347708</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1134,22 +1110,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,132 +1150,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>110542084</v>
-      </c>
-      <c r="B6" t="n">
-        <v>44333</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>102018</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Zygaena lonicerae</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Spenörtsbeståndet, Århult V Oskarshamn, Sm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>578045.6145036576</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6347707.986212344</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Oskarshamn</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Döderhult</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Leon Axelsson Widén</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Leon Axelsson Widén, Sture Ljungblom</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41442-2023 artfynd.xlsx
+++ b/artfynd/A 41442-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110542084</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110542050</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66630228</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,8 +1170,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110288930</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>